--- a/Dr.入力病名一覧.xlsx
+++ b/Dr.入力病名一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\cursor_project\orca_byoumei_post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE0158F-B7C7-4D64-B104-328859BB608D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6C5788-C341-4468-B343-78D2E67C1899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="405" windowWidth="21150" windowHeight="14385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="255" windowWidth="21150" windowHeight="14385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>ptid</t>
   </si>
@@ -64,19 +64,10 @@
     <t>感冒</t>
   </si>
   <si>
-    <t>130983</t>
-  </si>
-  <si>
-    <t>肺癌の疑い</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
     <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>131711</t>
   </si>
   <si>
     <t>両細菌性結膜炎</t>
@@ -90,11 +81,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>testc</t>
+    <t>中止（転医）</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>中止（転医）</t>
+    <t>16</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -498,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -529,7 +520,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -552,7 +543,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
@@ -575,7 +566,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -595,43 +586,30 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3">
         <v>46150</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3">
-        <v>46150</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>